--- a/tame_output/ON/bt/strategyON_20240407.xlsx
+++ b/tame_output/ON/bt/strategyON_20240407.xlsx
@@ -1002,7 +1002,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-506.1%</t>
+          <t>-506.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-205.6%</t>
+          <t>-205.8%</t>
         </is>
       </c>
     </row>
@@ -45849,10 +45849,10 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-3.444931218830872</v>
+        <v>-3.449509944290716</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.706347462083169</v>
+        <v>1.704515971899232</v>
       </c>
       <c r="F1926" t="n">
         <v>0.03908368176247767</v>

--- a/tame_output/ON/bt/strategyON_20240407.xlsx
+++ b/tame_output/ON/bt/strategyON_20240407.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.8%</t>
+          <t>115.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.6%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>497.0%</t>
+          <t>496.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-506.5%</t>
+          <t>-533.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-205.8%</t>
+          <t>-216.4%</t>
         </is>
       </c>
     </row>
@@ -45849,10 +45849,10 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-3.449509944290716</v>
+        <v>-3.714446447945081</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.704515971899232</v>
+        <v>1.598541370437486</v>
       </c>
       <c r="F1926" t="n">
         <v>0.03908368176247767</v>

--- a/tame_output/ON/bt/strategyON_20240407.xlsx
+++ b/tame_output/ON/bt/strategyON_20240407.xlsx
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317622</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737176</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>

--- a/tame_output/ON/bt/strategyON_20240407.xlsx
+++ b/tame_output/ON/bt/strategyON_20240407.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,75 +801,75 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-30.8%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.3%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.1%</t>
+          <t>134.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>496.4%</t>
+          <t>496.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-135.2%</t>
+          <t>-165.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1926"/>
+  <dimension ref="A1:G1927"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.433481714093779</v>
+        <v>3.821589933837687</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
@@ -45859,6 +45859,29 @@
       </c>
       <c r="G1926" t="n">
         <v>3.108126582986753</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="2" t="n">
+        <v>45389</v>
+      </c>
+      <c r="B1927" t="n">
+        <v>3.442540475014185</v>
+      </c>
+      <c r="C1927" t="n">
+        <v>2.808484210064536</v>
+      </c>
+      <c r="D1927" t="n">
+        <v>-3.714446447945081</v>
+      </c>
+      <c r="E1927" t="n">
+        <v>1.598541370437486</v>
+      </c>
+      <c r="F1927" t="n">
+        <v>0.03908368176247767</v>
+      </c>
+      <c r="G1927" t="n">
+        <v>2.801548007050904</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240407.xlsx
+++ b/tame_output/ON/bt/strategyON_20240407.xlsx
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>

--- a/tame_output/ON/bt/strategyON_20240407.xlsx
+++ b/tame_output/ON/bt/strategyON_20240407.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>52.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,45 +791,45 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>2.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>115.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.0%</t>
+          <t>133.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.2%</t>
+          <t>-53.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-71.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>496.5%</t>
+          <t>502.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-533.0%</t>
+          <t>-505.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-41.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-216.4%</t>
+          <t>-205.4%</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.9%</t>
+          <t>-132.2%</t>
         </is>
       </c>
     </row>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.406545913352809</v>
+        <v>-7.386978258146441</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1559039040378178</v>
+        <v>0.1637309661203648</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.629197193151051</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.42026077767792</v>
+        <v>-7.400693122471552</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.1465175234534684</v>
+        <v>0.1543445855360157</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.629197193151051</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.7330855769229</v>
+        <v>-7.713517921716532</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.01979252381047747</v>
+        <v>0.02761958589302482</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.629197193151051</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.737898615388237</v>
+        <v>-7.718330960181869</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.02164628435355098</v>
+        <v>0.02947334643609789</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.630743827853836</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.171247723498473</v>
+        <v>-8.151680068292105</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1557196634249465</v>
+        <v>-0.1478926013423996</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.630743827853836</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.554249112241104</v>
+        <v>-8.534681457034736</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3090223202435833</v>
+        <v>-0.301195258161036</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.630743827853836</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.929234438412381</v>
+        <v>-8.909666783206013</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4564449347406638</v>
+        <v>-0.4486178726581169</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.005729154025114</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.288764760916383</v>
+        <v>-9.269197105710015</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5949067604442142</v>
+        <v>-0.5870796983616673</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.005729154025114</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.615164789581396</v>
+        <v>-9.595597134375028</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7175507519530422</v>
+        <v>-0.7097236898704948</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.332129182690127</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.608688642787836</v>
+        <v>-9.589120987581468</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7119185426138492</v>
+        <v>-0.7040914805313023</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.325653035896567</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.604997717831425</v>
+        <v>-9.585430062625058</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7104421726312853</v>
+        <v>-0.7026151105487379</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.325653035896567</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.809255893161289</v>
+        <v>-9.789688237954921</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7866322456445882</v>
+        <v>-0.7788051835620413</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.453291980510556</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.969894919649654</v>
+        <v>-9.950327264443287</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8464053017554982</v>
+        <v>-0.8385782396729513</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.568025453512952</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.896425087982205</v>
+        <v>-9.876857432775838</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8016456675950976</v>
+        <v>-0.7938186055125502</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.494555621845504</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.07154950536875</v>
+        <v>-10.05198185016238</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8571402138021984</v>
+        <v>-0.8493131517196506</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.669680039232047</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.30600159938324</v>
+        <v>-10.28643394417687</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9581402163095896</v>
+        <v>-0.9503131542270427</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.669680039232047</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.59380544392048</v>
+        <v>-10.57423778871411</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.079933944898462</v>
+        <v>-1.072106882815915</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.957483883769286</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.8236298910843</v>
+        <v>-10.80406223587793</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.170747933925435</v>
+        <v>-1.162920871842888</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.120131420839446</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.05565881082056</v>
+        <v>-11.0360911556142</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.260865773190825</v>
+        <v>-1.253038711108279</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.182144118027869</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.00364329685175</v>
+        <v>-10.98407564164538</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.2360692319169</v>
+        <v>-1.228242169834352</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.182144118027869</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.14531513857587</v>
+        <v>-11.1257474833695</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.294213195505289</v>
+        <v>-1.286386133422742</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.182144118027869</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.24422187903515</v>
+        <v>-11.22465422382878</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.318722481524127</v>
+        <v>-1.31089541944158</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.281050858487145</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.04506977179805</v>
+        <v>-11.02550211659168</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.25211277227597</v>
+        <v>-1.244285710193423</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.115728332537332</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.81922461907864</v>
+        <v>-10.79965696387227</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.152195638151997</v>
+        <v>-1.14436857606945</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.073801656950168</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.53294980675594</v>
+        <v>-10.51338215154957</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.03654656866686</v>
+        <v>-1.028719506584313</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.073801656950168</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.58584509480023</v>
+        <v>-10.56627743959386</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.055070909722467</v>
+        <v>-1.047243847639921</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.068846310861722</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.30193636387148</v>
+        <v>-10.28236870866511</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9357737131123312</v>
+        <v>-0.9279466510297842</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.068846310861722</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.05494911367853</v>
+        <v>-10.03538145847216</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8467160754290157</v>
+        <v>-0.8388890133464688</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.82185906066877</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.791112246474457</v>
+        <v>-9.771544591268091</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7510648098602952</v>
+        <v>-0.7432377477777488</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.82185906066877</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.523870445606059</v>
+        <v>-9.504302790399693</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6460026500123099</v>
+        <v>-0.6381755879297635</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.82185906066877</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.248061282205574</v>
+        <v>-9.228493626999208</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5359792996255766</v>
+        <v>-0.5281522375430305</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.732839752390036</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.224107741229616</v>
+        <v>-9.20454008602325</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5257293770897</v>
+        <v>-0.5179023150071536</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.708886211414079</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.96004780290682</v>
+        <v>-8.940480147700454</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4333657179223334</v>
+        <v>-0.4255386558397869</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.444826273091283</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.252968179401982</v>
+        <v>-8.233400524195616</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1533209021806994</v>
+        <v>-0.1454938400981529</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.444826273091283</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.00332714941603</v>
+        <v>-7.983759494209664</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.05312086629847723</v>
+        <v>-0.04529380421593077</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.195185243105331</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.748785250074954</v>
+        <v>-7.729217594868588</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.04806271465871026</v>
+        <v>0.05588977674125672</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.940643343764255</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.515304027845356</v>
+        <v>-7.49573637263899</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1493796323884018</v>
+        <v>0.1572066944709483</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.707162121534657</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.335595497701483</v>
+        <v>-7.316027842495117</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2183708341329917</v>
+        <v>0.2261978962155382</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.649990617371961</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.203320024070597</v>
+        <v>-7.183752368864231</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2666485103323732</v>
+        <v>0.2744755724149197</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.517715143741074</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.012720349397444</v>
+        <v>-6.993152694191078</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3457034408892712</v>
+        <v>0.3535305029718177</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.327115469067921</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.763720550713863</v>
+        <v>-6.744152895507497</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4582097015863624</v>
+        <v>0.4660367636689089</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.327115469067921</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.869310540486968</v>
+        <v>-6.849742885280602</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2879977760779018</v>
+        <v>0.2958248381604482</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.432705458841026</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.888045442605565</v>
+        <v>-6.868477787399199</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3290481571075494</v>
+        <v>0.3368752191900959</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.432705458841026</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.611307267934752</v>
+        <v>-6.591739612728386</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4431224389618693</v>
+        <v>0.4509495010444158</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.2508887977311</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.484414861499681</v>
+        <v>-6.464847206293316</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.485165415282419</v>
+        <v>0.4929924773649654</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.12399639129603</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.296827353589755</v>
+        <v>-6.277259698383389</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5532398063512964</v>
+        <v>0.5610668684338429</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.12399639129603</v>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.054678960135897</v>
+        <v>-6.035111304929531</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.6645615181139828</v>
+        <v>0.6723885801965293</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.12399639129603</v>
@@ -45573,10 +45573,10 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.991449588367549</v>
+        <v>-5.971881933161183</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6843853872805172</v>
+        <v>0.6922124493630637</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.12399639129603</v>
@@ -45596,10 +45596,10 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.804961895990543</v>
+        <v>-5.785394240784177</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.7564785582418967</v>
+        <v>0.7643056203244432</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.9375086989190236</v>
@@ -45619,10 +45619,10 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.783812697087099</v>
+        <v>-5.764245041880733</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.7726392160405995</v>
+        <v>0.780466278123146</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.9163595000155802</v>
@@ -45642,10 +45642,10 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.540047255103655</v>
+        <v>-5.520479599897289</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.865926101181028</v>
+        <v>0.8737531632635744</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.9163595000155802</v>
@@ -45665,10 +45665,10 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.276019187910395</v>
+        <v>-5.256451532704029</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.9736616419783481</v>
+        <v>0.9814887040608946</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.7144941011996266</v>
@@ -45688,10 +45688,10 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.02616879396132</v>
+        <v>-5.006601138754954</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.06634387454168</v>
+        <v>1.074170936624226</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.7144941011996266</v>
@@ -45711,10 +45711,10 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.722601304957341</v>
+        <v>-4.703033649750975</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.19136999366392</v>
+        <v>1.199197055746467</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.7144941011996266</v>
@@ -45734,10 +45734,10 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.649121396105327</v>
+        <v>-4.629553740898961</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.23408946325928</v>
+        <v>1.241916525341826</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.6410141923476123</v>
@@ -45757,10 +45757,10 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.424088396436504</v>
+        <v>-4.404520741230138</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.323123140743106</v>
+        <v>1.330950202825652</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.4159811926787894</v>
@@ -45780,10 +45780,10 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.209454018800098</v>
+        <v>-4.189886363593732</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.413671692851986</v>
+        <v>1.421498754934532</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.2013468150423826</v>
@@ -45803,10 +45803,10 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.942853661825746</v>
+        <v>-3.92328600661938</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.501506094425522</v>
+        <v>1.509333156508069</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.2013468150423826</v>
@@ -45826,10 +45826,10 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-3.702423165020885</v>
+        <v>-3.682855509814519</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.599421369772344</v>
+        <v>1.60724843185489</v>
       </c>
       <c r="F1925" t="n">
         <v>0.03908368176247767</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837687</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-3.714446447945081</v>
+        <v>-3.440064702165074</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.598541370437486</v>
+        <v>1.708294068749488</v>
       </c>
       <c r="F1926" t="n">
         <v>0.03908368176247767</v>
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.442540475014185</v>
+        <v>3.805817121350834</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.808484210064536</v>
+        <v>3.144808745800142</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.714446447945081</v>
+        <v>-3.440064702165074</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.598541370437486</v>
+        <v>1.708294068749488</v>
       </c>
       <c r="F1927" t="n">
         <v>0.03908368176247767</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.801548007050904</v>
+        <v>3.13787254278651</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240407.xlsx
+++ b/tame_output/ON/bt/strategyON_20240407.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.2%</t>
+          <t>502.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-505.6%</t>
+          <t>-507.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-205.4%</t>
+          <t>-206.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-220.1%</t>
+          <t>-222.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-132.2%</t>
+          <t>-136.5%</t>
         </is>
       </c>
     </row>
@@ -45869,19 +45869,19 @@
         <v>3.805817121350834</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.144808745800142</v>
+        <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.440064702165074</v>
+        <v>-3.456977766611534</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.708294068749488</v>
+        <v>1.702207426888245</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.03908368176247767</v>
+        <v>0.0156923627285307</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.13787254278651</v>
+        <v>3.094770375483724</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240407.xlsx
+++ b/tame_output/ON/bt/strategyON_20240407.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.6%</t>
+          <t>116.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.9%</t>
+          <t>136.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-634.3%</t>
+          <t>-665.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>-54.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.1%</t>
+          <t>497.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-507.3%</t>
+          <t>-542.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-254.1%</t>
+          <t>-260.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-42.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-46.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-206.0%</t>
+          <t>-220.1%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1318,17 +1318,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.7%</t>
+          <t>-153.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-222.4%</t>
+          <t>-220.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-136.5%</t>
+          <t>-135.6%</t>
         </is>
       </c>
     </row>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.386978258146441</v>
+        <v>-7.406545913352809</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1637309661203648</v>
+        <v>0.1559039040378178</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.629197193151051</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.400693122471552</v>
+        <v>-7.760980985395211</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.1543445855360157</v>
+        <v>0.01022944036655238</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.629197193151051</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.713517921716532</v>
+        <v>-8.073805784640189</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.02761958589302482</v>
+        <v>-0.1164955592764385</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.629197193151051</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.718330960181869</v>
+        <v>-8.078618823105526</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.02947334643609789</v>
+        <v>-0.1146417987333646</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.630743827853836</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.151680068292105</v>
+        <v>-8.511967931215761</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1478926013423996</v>
+        <v>-0.292007746511862</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.630743827853836</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.534681457034736</v>
+        <v>-8.894969319958392</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.301195258161036</v>
+        <v>-0.4453104033304984</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.630743827853836</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.447750501317622</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.909666783206013</v>
+        <v>-9.269954646129669</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4486178726581169</v>
+        <v>-0.5927330178275789</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.005729154025114</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737176</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.269197105710015</v>
+        <v>-9.629484968633671</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5870796983616673</v>
+        <v>-0.7311948435311297</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.005729154025114</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341319</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.595597134375028</v>
+        <v>-9.955884997298684</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7097236898704948</v>
+        <v>-0.8538388350399573</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.332129182690127</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.589120987581468</v>
+        <v>-9.949408850505124</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7040914805313023</v>
+        <v>-0.8482066257007648</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.325653035896567</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.585430062625058</v>
+        <v>-9.945717925548713</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7026151105487379</v>
+        <v>-0.8467302557182004</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.325653035896567</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.789688237954921</v>
+        <v>-10.14997610087858</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7788051835620413</v>
+        <v>-0.9229203287315038</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.453291980510556</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.950327264443287</v>
+        <v>-10.31061512736694</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8385782396729513</v>
+        <v>-0.9826933848424138</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.568025453512952</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.876857432775838</v>
+        <v>-10.23714529569949</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7938186055125502</v>
+        <v>-0.9379337506820127</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.494555621845504</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.05198185016238</v>
+        <v>-10.41226971308604</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8493131517196506</v>
+        <v>-0.993428296889113</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.669680039232047</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.28643394417687</v>
+        <v>-10.64672180710053</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9503131542270427</v>
+        <v>-1.094428299396505</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.669680039232047</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.57423778871411</v>
+        <v>-10.93452565163776</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.072106882815915</v>
+        <v>-1.216222027985376</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.957483883769286</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.80406223587793</v>
+        <v>-11.16435009880159</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.162920871842888</v>
+        <v>-1.307036017012351</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.120131420839446</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.0360911556142</v>
+        <v>-11.39637901853785</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.253038711108279</v>
+        <v>-1.39715385627774</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.182144118027869</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.98407564164538</v>
+        <v>-11.34436350456904</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.228242169834352</v>
+        <v>-1.372357315003814</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.182144118027869</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.1257474833695</v>
+        <v>-11.48603534629316</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.286386133422742</v>
+        <v>-1.430501278592204</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.182144118027869</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.22465422382878</v>
+        <v>-11.58494208675243</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.31089541944158</v>
+        <v>-1.455010564611043</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.281050858487145</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.02550211659168</v>
+        <v>-11.38578997951534</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.244285710193423</v>
+        <v>-1.388400855362886</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.115728332537332</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.79965696387227</v>
+        <v>-11.15994482679593</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.14436857606945</v>
+        <v>-1.288483721238913</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.073801656950168</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.51338215154957</v>
+        <v>-10.87367001447323</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.028719506584313</v>
+        <v>-1.172834651753776</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.073801656950168</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.56627743959386</v>
+        <v>-10.92656530251752</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.047243847639921</v>
+        <v>-1.191358992809383</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.068846310861722</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.28236870866511</v>
+        <v>-10.64265657158877</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9279466510297842</v>
+        <v>-1.072061796199247</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.068846310861722</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.03538145847216</v>
+        <v>-10.39566932139582</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8388890133464688</v>
+        <v>-0.9830041585159313</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.82185906066877</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.771544591268091</v>
+        <v>-10.13183245419175</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7432377477777488</v>
+        <v>-0.8873528929472108</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.82185906066877</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.504302790399693</v>
+        <v>-9.864590653323349</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6381755879297635</v>
+        <v>-0.7822907330992259</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.82185906066877</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.228493626999208</v>
+        <v>-9.588781489922864</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5281522375430305</v>
+        <v>-0.6722673827124925</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.732839752390036</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.20454008602325</v>
+        <v>-9.564827948946906</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5179023150071536</v>
+        <v>-0.662017460176616</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.708886211414079</v>
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.940480147700454</v>
+        <v>-9.546351443766783</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4255386558397869</v>
+        <v>-0.6678871742663186</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.444826273091283</v>
+        <v>-2.690409706233956</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.684114063699373</v>
+        <v>1.536764003813769</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.233400524195616</v>
+        <v>-8.839271820261946</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1454938400981529</v>
+        <v>-0.3878423585246846</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.444826273091283</v>
+        <v>-2.690409706233956</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.681327030039072</v>
+        <v>1.533976970153468</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.983759494209664</v>
+        <v>-8.589630790275994</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.04529380421593077</v>
+        <v>-0.2876423226424625</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.195185243105331</v>
+        <v>-2.440768676248005</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.831455271918484</v>
+        <v>1.68410521203288</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.729217594868588</v>
+        <v>-8.335088890934918</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.05588977674125672</v>
+        <v>-0.186458741685275</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.940643343764255</v>
+        <v>-2.186226776906929</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.983547232743887</v>
+        <v>1.836197172858282</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.49573637263899</v>
+        <v>-8.10160766870532</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1572066944709483</v>
+        <v>-0.0851418239555839</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.707162121534657</v>
+        <v>-1.95274555467733</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.131560394919498</v>
+        <v>1.984210335033894</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.316027842495117</v>
+        <v>-7.921899138561447</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2261978962155382</v>
+        <v>-0.01615062221099395</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.649990617371961</v>
+        <v>-1.895574050514634</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.162971087104157</v>
+        <v>2.015621027218552</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.183752368864231</v>
+        <v>-7.789623664930561</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2744755724149197</v>
+        <v>0.03212705398838755</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.517715143741074</v>
+        <v>-1.763298576883748</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.237703858029715</v>
+        <v>2.090353798144111</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.993152694191078</v>
+        <v>-7.599023990257408</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3535305029718177</v>
+        <v>0.1111819845452855</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.327115469067921</v>
+        <v>-1.572698902210595</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.354878723521244</v>
+        <v>2.20752866363564</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.744152895507497</v>
+        <v>-7.350024191573827</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4660367636689089</v>
+        <v>0.2236882452423767</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.327115469067921</v>
+        <v>-1.572698902210595</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.367785064744903</v>
+        <v>2.220435004859299</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.849742885280602</v>
+        <v>-7.455614181346932</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2958248381604482</v>
+        <v>0.05347631973391609</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.432705458841026</v>
+        <v>-1.678288891983699</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.176455141281822</v>
+        <v>2.029105081396217</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.868477787399199</v>
+        <v>-7.474349083465529</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3368752191900959</v>
+        <v>0.09452670076356373</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.432705458841026</v>
+        <v>-1.678288891983699</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.224999483158908</v>
+        <v>2.077649423273304</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.591739612728386</v>
+        <v>-7.197610908794717</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4509495010444158</v>
+        <v>0.2086009826178832</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.2508887977311</v>
+        <v>-1.496472230873773</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.337468491810858</v>
+        <v>2.190118431925254</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.464847206293316</v>
+        <v>-7.070718502359647</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4929924773649654</v>
+        <v>0.2506439589384333</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.12399639129603</v>
+        <v>-1.369579824438703</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.404889949418422</v>
+        <v>2.257539889532818</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.277259698383389</v>
+        <v>-6.88313099444972</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5610668684338429</v>
+        <v>0.3187183500073103</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.12399639129603</v>
+        <v>-1.369579824438703</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.397929337323329</v>
+        <v>2.250579277437724</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.035111304929531</v>
+        <v>-6.640982600995862</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.6723885801965293</v>
+        <v>0.4300400617699967</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.12399639129603</v>
+        <v>-1.369579824438703</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.412391691704472</v>
+        <v>2.265041631818868</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.971881933161183</v>
+        <v>-6.577753229227514</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6922124493630637</v>
+        <v>0.4498639309365311</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.12399639129603</v>
+        <v>-1.369579824438703</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.406923812163667</v>
+        <v>2.259573752278063</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.785394240784177</v>
+        <v>-6.391265536850508</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.7643056203244432</v>
+        <v>0.5219571018979106</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.9375086989190236</v>
+        <v>-1.183092132061697</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.516314521600447</v>
+        <v>2.368964461714843</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.764245041880733</v>
+        <v>-6.370116337947064</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.780466278123146</v>
+        <v>0.5381177596966134</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.9163595000155802</v>
+        <v>-1.161942933158254</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.536705019179839</v>
+        <v>2.389354959294235</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.520479599897289</v>
+        <v>-6.12635089596362</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.8737531632635744</v>
+        <v>0.6314046448370418</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.9163595000155802</v>
+        <v>-1.161942933158254</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.53248572752689</v>
+        <v>2.385135667641285</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.256451532704029</v>
+        <v>-5.86232282877036</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.9814887040608946</v>
+        <v>0.739140185634362</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.7144941011996266</v>
+        <v>-0.9600775343423003</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.655729280736478</v>
+        <v>2.508379220850874</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.006601138754954</v>
+        <v>-5.612472434821285</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.074170936624226</v>
+        <v>0.8318224181976941</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.7144941011996266</v>
+        <v>-0.9600775343423003</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.64847135572018</v>
+        <v>2.501121295834576</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.703033649750975</v>
+        <v>-5.308904945817306</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.199197055746467</v>
+        <v>0.9568485373199342</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.7144941011996266</v>
+        <v>-0.9600775343423003</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.652070479240829</v>
+        <v>2.504720419355225</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.629553740898961</v>
+        <v>-5.235425036965292</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.241916525341826</v>
+        <v>0.9995680069152937</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.6410141923476123</v>
+        <v>-0.8865976254902859</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.709485930606591</v>
+        <v>2.562135870720987</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.404520741230138</v>
+        <v>-5.010392037296469</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.330950202825652</v>
+        <v>1.08860168439912</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4159811926787894</v>
+        <v>-0.661564625821463</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.843526208024182</v>
+        <v>2.696176148138577</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.189886363593732</v>
+        <v>-4.795757659660063</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.421498754934532</v>
+        <v>1.179150236508</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.2013468150423826</v>
+        <v>-0.4469302481850562</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.977001635660343</v>
+        <v>2.829651575774739</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.92328600661938</v>
+        <v>-4.529157302685711</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.509333156508069</v>
+        <v>1.266984638081536</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.2013468150423826</v>
+        <v>-0.4469302481850562</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.958195894444139</v>
+        <v>2.810845834558535</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-3.682855509814519</v>
+        <v>-4.288726805880851</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.60724843185489</v>
+        <v>1.364899913428358</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.03908368176247767</v>
+        <v>-0.2064997513801959</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.104197269151932</v>
+        <v>2.956847209266328</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-3.440064702165074</v>
+        <v>-4.045935998231405</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.708294068749488</v>
+        <v>1.465945550322956</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.03908368176247767</v>
+        <v>-0.2064997513801959</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.108126582986753</v>
+        <v>2.960776523101148</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.805817121350834</v>
+        <v>3.474088693347393</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.456977766611534</v>
+        <v>-3.808706769357683</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.702207426888245</v>
+        <v>1.561515825789785</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.0156923627285307</v>
+        <v>0.03072947749352628</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.094770375483724</v>
+        <v>3.103792644342722</v>
       </c>
     </row>
   </sheetData>
